--- a/Liga 2021-22/cromos_laliga.xlsx
+++ b/Liga 2021-22/cromos_laliga.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuari\Documents\Cromos\Liga 2021-22\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2021-22\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7858416D-C45E-4D16-804A-295F146F39A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571CFE18-4969-4361-840A-15F63AA41E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="19" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -4391,7 +4391,7 @@
     <xf numFmtId="0" fontId="3" fillId="37" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -4402,9 +4402,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4426,6 +4423,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4752,9 +4752,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.28515625" customWidth="1"/>
+    <col min="1" max="1" width="38.33203125" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
@@ -4763,7 +4763,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
         <v>58</v>
       </c>
@@ -4771,7 +4771,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>59</v>
       </c>
@@ -4794,7 +4794,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>63</v>
       </c>
@@ -4815,14 +4815,14 @@
       </c>
       <c r="F3" s="28">
         <f>SUM('D. ALAVÉS'!F3:F29)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" s="33">
         <f>SUM('D. ALAVÉS'!G3:G29)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>64</v>
       </c>
@@ -4843,14 +4843,14 @@
       </c>
       <c r="F4" s="28">
         <f>SUM('ATHLETIC CLUB'!F3:F28)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="33">
         <f>SUM('ATHLETIC CLUB'!G3:G28)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>65</v>
       </c>
@@ -4871,14 +4871,14 @@
       </c>
       <c r="F5" s="28">
         <f>SUM('ATLÉTICO DE MADRID'!F3:F27)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" s="33">
         <f>SUM('ATLÉTICO DE MADRID'!G3:G27)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>66</v>
       </c>
@@ -4906,7 +4906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>67</v>
       </c>
@@ -4927,14 +4927,14 @@
       </c>
       <c r="F7" s="28">
         <f>SUM('REAL BETIS'!F3:F30)</f>
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G7" s="33">
         <f>SUM('REAL BETIS'!G3:G30)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>68</v>
       </c>
@@ -4955,14 +4955,14 @@
       </c>
       <c r="F8" s="28">
         <f>SUM('CADIZ CF'!F3:F28)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="33">
         <f>SUM('CADIZ CF'!G3:G28)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>69</v>
       </c>
@@ -4983,14 +4983,14 @@
       </c>
       <c r="F9" s="28">
         <f>SUM('RC CELTA'!F3:F26)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="33">
         <f>SUM('RC CELTA'!G3:G26)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>70</v>
       </c>
@@ -5011,14 +5011,14 @@
       </c>
       <c r="F10" s="28">
         <f>SUM('ELCHE CF'!F3:F28)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="33">
         <f>SUM('ELCHE CF'!G3:G28)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>71</v>
       </c>
@@ -5039,14 +5039,14 @@
       </c>
       <c r="F11" s="28">
         <f>SUM('RCD ESPANYOL'!F3:F26)</f>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G11" s="33">
         <f>SUM('RCD ESPANYOL'!G3:G26)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>72</v>
       </c>
@@ -5067,14 +5067,14 @@
       </c>
       <c r="F12" s="28">
         <f>SUM('GETAFE CF'!F3:F30)</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G12" s="33">
         <f>SUM('GETAFE CF'!G3:G30)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>73</v>
       </c>
@@ -5095,14 +5095,14 @@
       </c>
       <c r="F13" s="28">
         <f>SUM('GRANADA CF'!F3:F26)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G13" s="33">
         <f>SUM('GRANADA CF'!G3:G26)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>74</v>
       </c>
@@ -5123,14 +5123,14 @@
       </c>
       <c r="F14" s="28">
         <f>SUM('LEVANTE UD'!F3:F27)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" s="33">
         <f>SUM('LEVANTE UD'!G3:G27)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>75</v>
       </c>
@@ -5151,14 +5151,14 @@
       </c>
       <c r="F15" s="28">
         <f>SUM('REAL MADRID'!F3:F29)</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G15" s="33">
         <f>SUM('REAL MADRID'!G3:G29)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>76</v>
       </c>
@@ -5186,7 +5186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>77</v>
       </c>
@@ -5207,14 +5207,14 @@
       </c>
       <c r="F17" s="28">
         <f>SUM('C.A. OSASUNA'!F3:F28)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G17" s="33">
         <f>SUM('C.A. OSASUNA'!G3:G28)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>78</v>
       </c>
@@ -5235,14 +5235,14 @@
       </c>
       <c r="F18" s="28">
         <f>SUM('RAYO VALLECANO'!F3:F28)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18" s="33">
         <f>SUM('RAYO VALLECANO'!G3:G28)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>79</v>
       </c>
@@ -5270,7 +5270,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>80</v>
       </c>
@@ -5291,14 +5291,14 @@
       </c>
       <c r="F20" s="28">
         <f>SUM('SEVILLA FC'!F3:F26)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G20" s="33">
         <f>SUM('SEVILLA FC'!G3:G26)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>0</v>
       </c>
@@ -5326,7 +5326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>81</v>
       </c>
@@ -5354,7 +5354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>82</v>
       </c>
@@ -5375,14 +5375,14 @@
       </c>
       <c r="F23" s="28">
         <f>SUM('LEYENDAS LaLiga'!F3:F34)</f>
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G23" s="33">
         <f>SUM('LEYENDAS LaLiga'!G3:G34)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>83</v>
       </c>
@@ -5403,14 +5403,14 @@
       </c>
       <c r="F24" s="28">
         <f>SUM('FICHAJES DE INVIERNO'!F3:F68)</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G24" s="33">
         <f>SUM('FICHAJES DE INVIERNO'!G3:G68)</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>84</v>
       </c>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="F25" s="28">
         <f>SUM('50 ANIVERSARIO'!F3:F11)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="33">
         <f>SUM('50 ANIVERSARIO'!G3:G11)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>85</v>
       </c>
@@ -5466,7 +5466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>86</v>
       </c>
@@ -5488,20 +5488,20 @@
       </c>
       <c r="F27" s="30">
         <f t="shared" si="0"/>
-        <v>279</v>
+        <v>314</v>
       </c>
       <c r="G27" s="34">
         <f t="shared" si="0"/>
-        <v>135</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="37"/>
       <c r="B28" s="37"/>
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>87</v>
       </c>
@@ -5518,7 +5518,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -5528,15 +5528,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="45" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5559,7 +5559,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>493</v>
       </c>
@@ -5577,7 +5577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>495</v>
       </c>
@@ -5595,7 +5595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>497</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>499</v>
       </c>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>501</v>
       </c>
@@ -5653,7 +5653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>502</v>
       </c>
@@ -5673,7 +5673,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>504</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>506</v>
       </c>
@@ -5709,7 +5709,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>508</v>
       </c>
@@ -5727,7 +5727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>510</v>
       </c>
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>512</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>514</v>
       </c>
@@ -5789,7 +5789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>516</v>
       </c>
@@ -5811,7 +5811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>518</v>
       </c>
@@ -5829,7 +5829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>520</v>
       </c>
@@ -5847,7 +5847,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>522</v>
       </c>
@@ -5865,7 +5865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>524</v>
       </c>
@@ -5879,13 +5879,15 @@
       <c r="E19" s="14">
         <v>2</v>
       </c>
-      <c r="F19" s="31"/>
+      <c r="F19" s="31">
+        <v>1</v>
+      </c>
       <c r="G19" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>525</v>
       </c>
@@ -5907,7 +5909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>526</v>
       </c>
@@ -5925,7 +5927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>528</v>
       </c>
@@ -5943,7 +5945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>530</v>
       </c>
@@ -5965,7 +5967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>532</v>
       </c>
@@ -5981,7 +5983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>534</v>
       </c>
@@ -5999,7 +6001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>536</v>
       </c>
@@ -6017,7 +6019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>538</v>
       </c>
@@ -6039,7 +6041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>540</v>
       </c>
@@ -6066,7 +6068,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -6076,15 +6078,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="46" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6107,7 +6109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>542</v>
       </c>
@@ -6121,13 +6123,15 @@
       <c r="E3" s="14">
         <v>1</v>
       </c>
-      <c r="F3" s="31"/>
+      <c r="F3" s="31">
+        <v>1</v>
+      </c>
       <c r="G3" s="35">
         <f t="shared" ref="G3:G26" si="0">MAX(0,E3-IF(F3="",0,F3))</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>544</v>
       </c>
@@ -6142,14 +6146,14 @@
         <v>2</v>
       </c>
       <c r="F4" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>546</v>
       </c>
@@ -6171,7 +6175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>547</v>
       </c>
@@ -6189,7 +6193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>549</v>
       </c>
@@ -6211,7 +6215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>551</v>
       </c>
@@ -6229,7 +6233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>553</v>
       </c>
@@ -6251,7 +6255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>555</v>
       </c>
@@ -6269,7 +6273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>557</v>
       </c>
@@ -6291,7 +6295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>559</v>
       </c>
@@ -6313,7 +6317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>561</v>
       </c>
@@ -6331,7 +6335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>563</v>
       </c>
@@ -6353,7 +6357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>565</v>
       </c>
@@ -6369,7 +6373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>567</v>
       </c>
@@ -6389,7 +6393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>569</v>
       </c>
@@ -6409,7 +6413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>571</v>
       </c>
@@ -6427,7 +6431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>573</v>
       </c>
@@ -6441,13 +6445,15 @@
       <c r="E19" s="14">
         <v>1</v>
       </c>
-      <c r="F19" s="31"/>
+      <c r="F19" s="31">
+        <v>1</v>
+      </c>
       <c r="G19" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>575</v>
       </c>
@@ -6465,7 +6471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>577</v>
       </c>
@@ -6483,7 +6489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>579</v>
       </c>
@@ -6505,7 +6511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>580</v>
       </c>
@@ -6527,7 +6533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>582</v>
       </c>
@@ -6543,7 +6549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>584</v>
       </c>
@@ -6565,7 +6571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>585</v>
       </c>
@@ -6594,7 +6600,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -6604,15 +6610,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="48" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="47" t="s">
         <v>72</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6635,7 +6641,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>587</v>
       </c>
@@ -6653,7 +6659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>589</v>
       </c>
@@ -6667,13 +6673,15 @@
       <c r="E4" s="14">
         <v>1</v>
       </c>
-      <c r="F4" s="31"/>
+      <c r="F4" s="31">
+        <v>1</v>
+      </c>
       <c r="G4" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>591</v>
       </c>
@@ -6691,7 +6699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>592</v>
       </c>
@@ -6709,7 +6717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>594</v>
       </c>
@@ -6723,13 +6731,15 @@
       <c r="E7" s="14">
         <v>2</v>
       </c>
-      <c r="F7" s="31"/>
+      <c r="F7" s="31">
+        <v>1</v>
+      </c>
       <c r="G7" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>596</v>
       </c>
@@ -6749,7 +6759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>598</v>
       </c>
@@ -6771,7 +6781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>600</v>
       </c>
@@ -6787,7 +6797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>602</v>
       </c>
@@ -6807,7 +6817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>604</v>
       </c>
@@ -6827,7 +6837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>606</v>
       </c>
@@ -6845,7 +6855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>608</v>
       </c>
@@ -6867,7 +6877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>610</v>
       </c>
@@ -6887,7 +6897,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>612</v>
       </c>
@@ -6903,7 +6913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>614</v>
       </c>
@@ -6921,7 +6931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>616</v>
       </c>
@@ -6937,7 +6947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>617</v>
       </c>
@@ -6951,13 +6961,15 @@
       <c r="E19" s="14">
         <v>2</v>
       </c>
-      <c r="F19" s="31"/>
+      <c r="F19" s="31">
+        <v>1</v>
+      </c>
       <c r="G19" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>618</v>
       </c>
@@ -6975,7 +6987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>620</v>
       </c>
@@ -6997,7 +7009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>622</v>
       </c>
@@ -7015,7 +7027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>624</v>
       </c>
@@ -7033,7 +7045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>626</v>
       </c>
@@ -7051,7 +7063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>628</v>
       </c>
@@ -7069,7 +7081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>630</v>
       </c>
@@ -7087,7 +7099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>632</v>
       </c>
@@ -7109,7 +7121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>634</v>
       </c>
@@ -7129,7 +7141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>636</v>
       </c>
@@ -7145,7 +7157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
         <v>638</v>
       </c>
@@ -7174,7 +7186,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -7184,15 +7196,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
         <v>73</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7215,7 +7227,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>640</v>
       </c>
@@ -7237,7 +7249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>642</v>
       </c>
@@ -7255,7 +7267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>644</v>
       </c>
@@ -7273,7 +7285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>646</v>
       </c>
@@ -7295,7 +7307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>648</v>
       </c>
@@ -7313,7 +7325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>650</v>
       </c>
@@ -7333,7 +7345,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>652</v>
       </c>
@@ -7347,13 +7359,15 @@
       <c r="E9" s="14">
         <v>1</v>
       </c>
-      <c r="F9" s="31"/>
+      <c r="F9" s="31">
+        <v>1</v>
+      </c>
       <c r="G9" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>654</v>
       </c>
@@ -7369,7 +7383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>656</v>
       </c>
@@ -7391,7 +7405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>658</v>
       </c>
@@ -7409,7 +7423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>660</v>
       </c>
@@ -7429,7 +7443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>662</v>
       </c>
@@ -7451,7 +7465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>664</v>
       </c>
@@ -7471,7 +7485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>666</v>
       </c>
@@ -7489,7 +7503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>668</v>
       </c>
@@ -7507,7 +7521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>670</v>
       </c>
@@ -7525,7 +7539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>672</v>
       </c>
@@ -7543,7 +7557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>674</v>
       </c>
@@ -7561,7 +7575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>676</v>
       </c>
@@ -7579,7 +7593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>677</v>
       </c>
@@ -7597,7 +7611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>679</v>
       </c>
@@ -7611,13 +7625,15 @@
       <c r="E23" s="14">
         <v>2</v>
       </c>
-      <c r="F23" s="31"/>
+      <c r="F23" s="31">
+        <v>1</v>
+      </c>
       <c r="G23" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>681</v>
       </c>
@@ -7635,7 +7651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>682</v>
       </c>
@@ -7651,7 +7667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>684</v>
       </c>
@@ -7680,7 +7696,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -7690,15 +7706,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="36" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="48" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -7721,7 +7737,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>686</v>
       </c>
@@ -7741,7 +7757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>688</v>
       </c>
@@ -7759,7 +7775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>690</v>
       </c>
@@ -7781,7 +7797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>692</v>
       </c>
@@ -7803,7 +7819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>694</v>
       </c>
@@ -7825,7 +7841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>696</v>
       </c>
@@ -7847,7 +7863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>697</v>
       </c>
@@ -7865,7 +7881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>699</v>
       </c>
@@ -7881,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>701</v>
       </c>
@@ -7899,7 +7915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>703</v>
       </c>
@@ -7921,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>705</v>
       </c>
@@ -7941,7 +7957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>707</v>
       </c>
@@ -7957,7 +7973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>709</v>
       </c>
@@ -7977,7 +7993,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>711</v>
       </c>
@@ -7993,7 +8009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>713</v>
       </c>
@@ -8011,7 +8027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>715</v>
       </c>
@@ -8029,7 +8045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>717</v>
       </c>
@@ -8051,7 +8067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>718</v>
       </c>
@@ -8065,13 +8081,15 @@
       <c r="E20" s="14">
         <v>1</v>
       </c>
-      <c r="F20" s="31"/>
+      <c r="F20" s="31">
+        <v>1</v>
+      </c>
       <c r="G20" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>720</v>
       </c>
@@ -8093,7 +8111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>722</v>
       </c>
@@ -8111,7 +8129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>724</v>
       </c>
@@ -8131,7 +8149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>726</v>
       </c>
@@ -8149,7 +8167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>728</v>
       </c>
@@ -8167,7 +8185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>729</v>
       </c>
@@ -8183,7 +8201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>731</v>
       </c>
@@ -8210,7 +8228,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -8220,7 +8238,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="49" t="s">
         <v>75</v>
       </c>
@@ -8228,7 +8246,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8251,7 +8269,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>733</v>
       </c>
@@ -8269,7 +8287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>735</v>
       </c>
@@ -8284,14 +8302,14 @@
         <v>2</v>
       </c>
       <c r="F4" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>737</v>
       </c>
@@ -8309,7 +8327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>738</v>
       </c>
@@ -8327,7 +8345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>740</v>
       </c>
@@ -8345,7 +8363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>742</v>
       </c>
@@ -8367,7 +8385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>744</v>
       </c>
@@ -8385,7 +8403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>746</v>
       </c>
@@ -8405,7 +8423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>748</v>
       </c>
@@ -8423,7 +8441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>750</v>
       </c>
@@ -8439,7 +8457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>752</v>
       </c>
@@ -8457,7 +8475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>754</v>
       </c>
@@ -8477,7 +8495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>756</v>
       </c>
@@ -8499,7 +8517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>758</v>
       </c>
@@ -8521,7 +8539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>760</v>
       </c>
@@ -8543,7 +8561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>762</v>
       </c>
@@ -8558,14 +8576,14 @@
         <v>2</v>
       </c>
       <c r="F18" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>764</v>
       </c>
@@ -8587,7 +8605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>766</v>
       </c>
@@ -8607,7 +8625,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>768</v>
       </c>
@@ -8629,7 +8647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>770</v>
       </c>
@@ -8645,7 +8663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>772</v>
       </c>
@@ -8661,7 +8679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>774</v>
       </c>
@@ -8679,7 +8697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>776</v>
       </c>
@@ -8697,7 +8715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>777</v>
       </c>
@@ -8715,7 +8733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>778</v>
       </c>
@@ -8733,7 +8751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>780</v>
       </c>
@@ -8749,7 +8767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>782</v>
       </c>
@@ -8778,7 +8796,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -8788,15 +8806,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
         <v>76</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -8819,7 +8837,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>784</v>
       </c>
@@ -8837,7 +8855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>786</v>
       </c>
@@ -8855,7 +8873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>788</v>
       </c>
@@ -8873,7 +8891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>790</v>
       </c>
@@ -8895,7 +8913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>792</v>
       </c>
@@ -8913,7 +8931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>794</v>
       </c>
@@ -8931,7 +8949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>796</v>
       </c>
@@ -8949,7 +8967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>798</v>
       </c>
@@ -8967,7 +8985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>800</v>
       </c>
@@ -8989,7 +9007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>802</v>
       </c>
@@ -9007,7 +9025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>804</v>
       </c>
@@ -9023,7 +9041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>806</v>
       </c>
@@ -9041,7 +9059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>808</v>
       </c>
@@ -9057,7 +9075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>810</v>
       </c>
@@ -9075,7 +9093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>812</v>
       </c>
@@ -9095,7 +9113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>814</v>
       </c>
@@ -9111,7 +9129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>816</v>
       </c>
@@ -9129,7 +9147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>817</v>
       </c>
@@ -9147,7 +9165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>819</v>
       </c>
@@ -9169,7 +9187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>821</v>
       </c>
@@ -9191,7 +9209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>823</v>
       </c>
@@ -9207,7 +9225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>825</v>
       </c>
@@ -9225,7 +9243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>826</v>
       </c>
@@ -9243,7 +9261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>828</v>
       </c>
@@ -9261,7 +9279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>830</v>
       </c>
@@ -9290,7 +9308,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -9300,15 +9318,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9331,7 +9349,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>832</v>
       </c>
@@ -9345,13 +9363,15 @@
       <c r="E3" s="14">
         <v>5</v>
       </c>
-      <c r="F3" s="31"/>
+      <c r="F3" s="31">
+        <v>1</v>
+      </c>
       <c r="G3" s="35">
         <f t="shared" ref="G3:G28" si="0">MAX(0,E3-IF(F3="",0,F3))</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>834</v>
       </c>
@@ -9369,7 +9389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>836</v>
       </c>
@@ -9383,13 +9403,15 @@
       <c r="E5" s="14">
         <v>1</v>
       </c>
-      <c r="F5" s="31"/>
+      <c r="F5" s="31">
+        <v>1</v>
+      </c>
       <c r="G5" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>837</v>
       </c>
@@ -9411,7 +9433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>839</v>
       </c>
@@ -9425,13 +9447,15 @@
       <c r="E7" s="14">
         <v>1</v>
       </c>
-      <c r="F7" s="31"/>
+      <c r="F7" s="31">
+        <v>1</v>
+      </c>
       <c r="G7" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>841</v>
       </c>
@@ -9449,7 +9473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>843</v>
       </c>
@@ -9463,13 +9487,15 @@
       <c r="E9" s="14">
         <v>1</v>
       </c>
-      <c r="F9" s="31"/>
+      <c r="F9" s="31">
+        <v>1</v>
+      </c>
       <c r="G9" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>845</v>
       </c>
@@ -9485,7 +9511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>847</v>
       </c>
@@ -9503,7 +9529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>849</v>
       </c>
@@ -9521,7 +9547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>851</v>
       </c>
@@ -9539,7 +9565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>853</v>
       </c>
@@ -9555,7 +9581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>855</v>
       </c>
@@ -9573,7 +9599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>856</v>
       </c>
@@ -9595,7 +9621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>858</v>
       </c>
@@ -9615,7 +9641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>860</v>
       </c>
@@ -9633,7 +9659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>862</v>
       </c>
@@ -9651,7 +9677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>864</v>
       </c>
@@ -9667,7 +9693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>866</v>
       </c>
@@ -9685,7 +9711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>868</v>
       </c>
@@ -9703,7 +9729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>869</v>
       </c>
@@ -9723,7 +9749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>871</v>
       </c>
@@ -9739,7 +9765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>873</v>
       </c>
@@ -9761,7 +9787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>875</v>
       </c>
@@ -9779,7 +9805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>877</v>
       </c>
@@ -9795,7 +9821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>879</v>
       </c>
@@ -9824,7 +9850,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -9834,7 +9860,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="50" t="s">
         <v>78</v>
       </c>
@@ -9842,7 +9868,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -9865,7 +9891,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>881</v>
       </c>
@@ -9883,7 +9909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>883</v>
       </c>
@@ -9901,7 +9927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>885</v>
       </c>
@@ -9923,7 +9949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>887</v>
       </c>
@@ -9945,7 +9971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>889</v>
       </c>
@@ -9963,7 +9989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>891</v>
       </c>
@@ -9981,7 +10007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>893</v>
       </c>
@@ -10001,7 +10027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>895</v>
       </c>
@@ -10023,7 +10049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>897</v>
       </c>
@@ -10039,7 +10065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>899</v>
       </c>
@@ -10061,7 +10087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>901</v>
       </c>
@@ -10083,7 +10109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>903</v>
       </c>
@@ -10105,7 +10131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>904</v>
       </c>
@@ -10123,7 +10149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>906</v>
       </c>
@@ -10145,7 +10171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>908</v>
       </c>
@@ -10165,7 +10191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>910</v>
       </c>
@@ -10183,7 +10209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>912</v>
       </c>
@@ -10205,7 +10231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>913</v>
       </c>
@@ -10219,13 +10245,15 @@
       <c r="E20" s="14">
         <v>1</v>
       </c>
-      <c r="F20" s="31"/>
+      <c r="F20" s="31">
+        <v>1</v>
+      </c>
       <c r="G20" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>914</v>
       </c>
@@ -10247,7 +10275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>916</v>
       </c>
@@ -10265,7 +10293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>918</v>
       </c>
@@ -10283,7 +10311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>920</v>
       </c>
@@ -10305,7 +10333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>922</v>
       </c>
@@ -10327,7 +10355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>924</v>
       </c>
@@ -10347,7 +10375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>926</v>
       </c>
@@ -10363,7 +10391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>928</v>
       </c>
@@ -10390,7 +10418,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -10400,15 +10428,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="46" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -10431,7 +10459,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>930</v>
       </c>
@@ -10453,7 +10481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>932</v>
       </c>
@@ -10473,7 +10501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>934</v>
       </c>
@@ -10491,7 +10519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>936</v>
       </c>
@@ -10513,7 +10541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>938</v>
       </c>
@@ -10531,7 +10559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>940</v>
       </c>
@@ -10549,7 +10577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>942</v>
       </c>
@@ -10569,7 +10597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>944</v>
       </c>
@@ -10585,7 +10613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>946</v>
       </c>
@@ -10607,7 +10635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>948</v>
       </c>
@@ -10625,7 +10653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>950</v>
       </c>
@@ -10643,7 +10671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>952</v>
       </c>
@@ -10661,7 +10689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>954</v>
       </c>
@@ -10677,7 +10705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>956</v>
       </c>
@@ -10695,7 +10723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>958</v>
       </c>
@@ -10713,7 +10741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>959</v>
       </c>
@@ -10731,7 +10759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>961</v>
       </c>
@@ -10749,7 +10777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>963</v>
       </c>
@@ -10767,7 +10795,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>965</v>
       </c>
@@ -10789,7 +10817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>966</v>
       </c>
@@ -10807,7 +10835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>968</v>
       </c>
@@ -10825,7 +10853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>970</v>
       </c>
@@ -10843,7 +10871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>972</v>
       </c>
@@ -10859,7 +10887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>974</v>
       </c>
@@ -10877,7 +10905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>975</v>
       </c>
@@ -10906,18 +10934,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
         <v>88</v>
       </c>
@@ -10926,7 +10954,7 @@
       <c r="D1" s="37"/>
       <c r="E1" s="37"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>59</v>
       </c>
@@ -10952,7 +10980,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="17" t="s">
         <v>63</v>
       </c>
@@ -10975,7 +11003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>63</v>
       </c>
@@ -10998,7 +11026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
         <v>63</v>
       </c>
@@ -11021,7 +11049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
         <v>64</v>
       </c>
@@ -11044,7 +11072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19" t="s">
         <v>64</v>
       </c>
@@ -11067,7 +11095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="21" t="s">
         <v>64</v>
       </c>
@@ -11090,7 +11118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>65</v>
       </c>
@@ -11113,7 +11141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
         <v>65</v>
       </c>
@@ -11136,7 +11164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
         <v>65</v>
       </c>
@@ -11159,7 +11187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="17" t="s">
         <v>66</v>
       </c>
@@ -11182,7 +11210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19" t="s">
         <v>66</v>
       </c>
@@ -11205,7 +11233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
         <v>66</v>
       </c>
@@ -11228,7 +11256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
         <v>67</v>
       </c>
@@ -11251,7 +11279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19" t="s">
         <v>67</v>
       </c>
@@ -11274,7 +11302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
         <v>67</v>
       </c>
@@ -11297,7 +11325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
         <v>68</v>
       </c>
@@ -11320,7 +11348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
         <v>68</v>
       </c>
@@ -11343,7 +11371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
         <v>68</v>
       </c>
@@ -11366,7 +11394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>69</v>
       </c>
@@ -11389,7 +11417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19" t="s">
         <v>69</v>
       </c>
@@ -11412,7 +11440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="21" t="s">
         <v>69</v>
       </c>
@@ -11435,7 +11463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="17" t="s">
         <v>70</v>
       </c>
@@ -11458,7 +11486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
         <v>70</v>
       </c>
@@ -11481,7 +11509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
         <v>70</v>
       </c>
@@ -11504,7 +11532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
         <v>71</v>
       </c>
@@ -11527,7 +11555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19" t="s">
         <v>71</v>
       </c>
@@ -11550,7 +11578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
         <v>71</v>
       </c>
@@ -11573,7 +11601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>72</v>
       </c>
@@ -11596,7 +11624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19" t="s">
         <v>72</v>
       </c>
@@ -11619,7 +11647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="21" t="s">
         <v>72</v>
       </c>
@@ -11642,7 +11670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
         <v>73</v>
       </c>
@@ -11665,7 +11693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
         <v>73</v>
       </c>
@@ -11688,7 +11716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
         <v>73</v>
       </c>
@@ -11711,7 +11739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="17" t="s">
         <v>74</v>
       </c>
@@ -11734,7 +11762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19" t="s">
         <v>74</v>
       </c>
@@ -11757,7 +11785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
         <v>74</v>
       </c>
@@ -11780,7 +11808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="17" t="s">
         <v>75</v>
       </c>
@@ -11803,7 +11831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19" t="s">
         <v>75</v>
       </c>
@@ -11826,7 +11854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="21" t="s">
         <v>75</v>
       </c>
@@ -11849,7 +11877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="17" t="s">
         <v>76</v>
       </c>
@@ -11872,7 +11900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19" t="s">
         <v>76</v>
       </c>
@@ -11895,7 +11923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="21" t="s">
         <v>76</v>
       </c>
@@ -11918,7 +11946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="17" t="s">
         <v>77</v>
       </c>
@@ -11941,7 +11969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19" t="s">
         <v>77</v>
       </c>
@@ -11964,7 +11992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="21" t="s">
         <v>77</v>
       </c>
@@ -11987,7 +12015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="17" t="s">
         <v>78</v>
       </c>
@@ -12010,7 +12038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="19" t="s">
         <v>78</v>
       </c>
@@ -12033,7 +12061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="21" t="s">
         <v>78</v>
       </c>
@@ -12056,7 +12084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
         <v>79</v>
       </c>
@@ -12079,7 +12107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="19" t="s">
         <v>79</v>
       </c>
@@ -12102,7 +12130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="21" t="s">
         <v>79</v>
       </c>
@@ -12125,7 +12153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
         <v>80</v>
       </c>
@@ -12148,7 +12176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="19" t="s">
         <v>80</v>
       </c>
@@ -12171,7 +12199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="21" t="s">
         <v>80</v>
       </c>
@@ -12194,7 +12222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="17" t="s">
         <v>0</v>
       </c>
@@ -12217,7 +12245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="19" t="s">
         <v>0</v>
       </c>
@@ -12240,7 +12268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="21" t="s">
         <v>0</v>
       </c>
@@ -12263,7 +12291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="17" t="s">
         <v>81</v>
       </c>
@@ -12286,7 +12314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="19" t="s">
         <v>81</v>
       </c>
@@ -12309,7 +12337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="21" t="s">
         <v>81</v>
       </c>
@@ -12343,7 +12371,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -12353,7 +12381,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="51" t="s">
         <v>80</v>
       </c>
@@ -12361,7 +12389,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12384,7 +12412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>977</v>
       </c>
@@ -12406,7 +12434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>979</v>
       </c>
@@ -12428,7 +12456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>981</v>
       </c>
@@ -12446,7 +12474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>983</v>
       </c>
@@ -12468,7 +12496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>985</v>
       </c>
@@ -12486,7 +12514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>987</v>
       </c>
@@ -12504,7 +12532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>989</v>
       </c>
@@ -12518,13 +12546,15 @@
       <c r="E9" s="14">
         <v>4</v>
       </c>
-      <c r="F9" s="31"/>
+      <c r="F9" s="31">
+        <v>1</v>
+      </c>
       <c r="G9" s="35">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>991</v>
       </c>
@@ -12542,7 +12572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>993</v>
       </c>
@@ -12564,7 +12594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>994</v>
       </c>
@@ -12580,7 +12610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>996</v>
       </c>
@@ -12598,7 +12628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>998</v>
       </c>
@@ -12620,7 +12650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>1000</v>
       </c>
@@ -12638,7 +12668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>1002</v>
       </c>
@@ -12660,7 +12690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>1003</v>
       </c>
@@ -12674,13 +12704,15 @@
       <c r="E17" s="14">
         <v>1</v>
       </c>
-      <c r="F17" s="31"/>
+      <c r="F17" s="31">
+        <v>1</v>
+      </c>
       <c r="G17" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>1005</v>
       </c>
@@ -12696,7 +12728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>1007</v>
       </c>
@@ -12718,7 +12750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>1009</v>
       </c>
@@ -12736,7 +12768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>1011</v>
       </c>
@@ -12758,7 +12790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>1013</v>
       </c>
@@ -12778,7 +12810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>1015</v>
       </c>
@@ -12798,7 +12830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>1017</v>
       </c>
@@ -12820,7 +12852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>1019</v>
       </c>
@@ -12840,7 +12872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>1021</v>
       </c>
@@ -12869,7 +12901,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -12879,7 +12911,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
         <v>0</v>
       </c>
@@ -12887,7 +12919,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -12910,7 +12942,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>8</v>
       </c>
@@ -12928,7 +12960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>11</v>
       </c>
@@ -12946,7 +12978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>13</v>
       </c>
@@ -12968,7 +13000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>15</v>
       </c>
@@ -12990,7 +13022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>17</v>
       </c>
@@ -13012,7 +13044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>19</v>
       </c>
@@ -13030,7 +13062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>21</v>
       </c>
@@ -13052,7 +13084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>23</v>
       </c>
@@ -13070,7 +13102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>25</v>
       </c>
@@ -13090,7 +13122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>27</v>
       </c>
@@ -13108,7 +13140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -13126,7 +13158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>30</v>
       </c>
@@ -13142,7 +13174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>32</v>
       </c>
@@ -13164,7 +13196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>34</v>
       </c>
@@ -13186,7 +13218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>36</v>
       </c>
@@ -13204,7 +13236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>38</v>
       </c>
@@ -13222,7 +13254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>40</v>
       </c>
@@ -13242,7 +13274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>42</v>
       </c>
@@ -13264,7 +13296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>44</v>
       </c>
@@ -13282,7 +13314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>46</v>
       </c>
@@ -13300,7 +13332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>48</v>
       </c>
@@ -13322,7 +13354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>50</v>
       </c>
@@ -13342,7 +13374,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>52</v>
       </c>
@@ -13360,7 +13392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>54</v>
       </c>
@@ -13376,7 +13408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>56</v>
       </c>
@@ -13403,7 +13435,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -13413,15 +13445,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="43" t="s">
         <v>81</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13444,7 +13476,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>1023</v>
       </c>
@@ -13466,7 +13498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>1025</v>
       </c>
@@ -13484,7 +13516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>1027</v>
       </c>
@@ -13506,7 +13538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>1028</v>
       </c>
@@ -13528,7 +13560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>1030</v>
       </c>
@@ -13546,7 +13578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>1032</v>
       </c>
@@ -13568,7 +13600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>1034</v>
       </c>
@@ -13584,7 +13616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>1036</v>
       </c>
@@ -13602,7 +13634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>1038</v>
       </c>
@@ -13620,7 +13652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>1040</v>
       </c>
@@ -13636,7 +13668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>1042</v>
       </c>
@@ -13656,7 +13688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>1044</v>
       </c>
@@ -13674,7 +13706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>1046</v>
       </c>
@@ -13692,7 +13724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>1048</v>
       </c>
@@ -13710,7 +13742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>1050</v>
       </c>
@@ -13728,7 +13760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>1052</v>
       </c>
@@ -13746,7 +13778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>1054</v>
       </c>
@@ -13764,7 +13796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>1056</v>
       </c>
@@ -13782,7 +13814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>1058</v>
       </c>
@@ -13802,7 +13834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>1060</v>
       </c>
@@ -13820,7 +13852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>1062</v>
       </c>
@@ -13838,7 +13870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>1063</v>
       </c>
@@ -13856,7 +13888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>1065</v>
       </c>
@@ -13872,7 +13904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>1067</v>
       </c>
@@ -13890,7 +13922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>1069</v>
       </c>
@@ -13919,7 +13951,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -13929,7 +13961,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="53" t="s">
         <v>82</v>
       </c>
@@ -13937,7 +13969,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -13960,7 +13992,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>1071</v>
       </c>
@@ -13978,7 +14010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>1073</v>
       </c>
@@ -13996,7 +14028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>1075</v>
       </c>
@@ -14018,7 +14050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>1077</v>
       </c>
@@ -14033,14 +14065,14 @@
         <v>3</v>
       </c>
       <c r="F6" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>1079</v>
       </c>
@@ -14062,7 +14094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>1081</v>
       </c>
@@ -14080,7 +14112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>1083</v>
       </c>
@@ -14102,7 +14134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>1085</v>
       </c>
@@ -14124,7 +14156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>1087</v>
       </c>
@@ -14146,7 +14178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>1089</v>
       </c>
@@ -14168,7 +14200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>1091</v>
       </c>
@@ -14186,7 +14218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>1093</v>
       </c>
@@ -14204,7 +14236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>1095</v>
       </c>
@@ -14226,7 +14258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>1097</v>
       </c>
@@ -14248,7 +14280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>1099</v>
       </c>
@@ -14263,14 +14295,14 @@
         <v>4</v>
       </c>
       <c r="F17" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G17" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>1101</v>
       </c>
@@ -14292,7 +14324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>1103</v>
       </c>
@@ -14307,14 +14339,14 @@
         <v>4</v>
       </c>
       <c r="F19" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>1105</v>
       </c>
@@ -14336,7 +14368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>1107</v>
       </c>
@@ -14358,7 +14390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>1109</v>
       </c>
@@ -14376,7 +14408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>1111</v>
       </c>
@@ -14398,7 +14430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>1113</v>
       </c>
@@ -14416,7 +14448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>1115</v>
       </c>
@@ -14434,7 +14466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>1117</v>
       </c>
@@ -14456,7 +14488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>1119</v>
       </c>
@@ -14478,7 +14510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>1121</v>
       </c>
@@ -14496,7 +14528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>1123</v>
       </c>
@@ -14518,7 +14550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
         <v>1125</v>
       </c>
@@ -14540,7 +14572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>1127</v>
       </c>
@@ -14555,14 +14587,14 @@
         <v>3</v>
       </c>
       <c r="F31" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
         <v>1129</v>
       </c>
@@ -14584,7 +14616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>1131</v>
       </c>
@@ -14606,7 +14638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>1133</v>
       </c>
@@ -14635,7 +14667,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:G68"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -14645,7 +14677,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
         <v>83</v>
       </c>
@@ -14653,7 +14685,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -14676,7 +14708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>1135</v>
       </c>
@@ -14694,7 +14726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>1137</v>
       </c>
@@ -14716,7 +14748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>1139</v>
       </c>
@@ -14734,7 +14766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>1141</v>
       </c>
@@ -14756,7 +14788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>1143</v>
       </c>
@@ -14778,7 +14810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>1145</v>
       </c>
@@ -14798,7 +14830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>1147</v>
       </c>
@@ -14818,7 +14850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>1149</v>
       </c>
@@ -14836,7 +14868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>1151</v>
       </c>
@@ -14854,7 +14886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>1153</v>
       </c>
@@ -14872,7 +14904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>1155</v>
       </c>
@@ -14890,7 +14922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>1157</v>
       </c>
@@ -14908,7 +14940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>1159</v>
       </c>
@@ -14928,7 +14960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>1161</v>
       </c>
@@ -14946,7 +14978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>1163</v>
       </c>
@@ -14966,7 +14998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>1165</v>
       </c>
@@ -14984,7 +15016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>1167</v>
       </c>
@@ -14998,13 +15030,15 @@
       <c r="E19" s="14">
         <v>1</v>
       </c>
-      <c r="F19" s="31"/>
+      <c r="F19" s="31">
+        <v>1</v>
+      </c>
       <c r="G19" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>1169</v>
       </c>
@@ -15026,7 +15060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>1171</v>
       </c>
@@ -15048,7 +15082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>1173</v>
       </c>
@@ -15066,7 +15100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>1175</v>
       </c>
@@ -15084,7 +15118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>1177</v>
       </c>
@@ -15106,7 +15140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>1179</v>
       </c>
@@ -15124,7 +15158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>1181</v>
       </c>
@@ -15142,7 +15176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>1183</v>
       </c>
@@ -15156,13 +15190,15 @@
       <c r="E27" s="14">
         <v>1</v>
       </c>
-      <c r="F27" s="31"/>
+      <c r="F27" s="31">
+        <v>1</v>
+      </c>
       <c r="G27" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>1185</v>
       </c>
@@ -15177,14 +15213,14 @@
         <v>3</v>
       </c>
       <c r="F28" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>1187</v>
       </c>
@@ -15202,7 +15238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
         <v>1189</v>
       </c>
@@ -15220,7 +15256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
         <v>1191</v>
       </c>
@@ -15238,7 +15274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="15" t="s">
         <v>1193</v>
       </c>
@@ -15256,7 +15292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>1195</v>
       </c>
@@ -15274,7 +15310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="15" t="s">
         <v>1197</v>
       </c>
@@ -15296,7 +15332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>1199</v>
       </c>
@@ -15314,7 +15350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="15" t="s">
         <v>1201</v>
       </c>
@@ -15332,7 +15368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>1203</v>
       </c>
@@ -15350,7 +15386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="15" t="s">
         <v>1205</v>
       </c>
@@ -15368,7 +15404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
         <v>1207</v>
       </c>
@@ -15386,7 +15422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="15" t="s">
         <v>1209</v>
       </c>
@@ -15404,7 +15440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11" t="s">
         <v>1211</v>
       </c>
@@ -15422,7 +15458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="15" t="s">
         <v>1213</v>
       </c>
@@ -15444,7 +15480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11" t="s">
         <v>1215</v>
       </c>
@@ -15462,7 +15498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="15" t="s">
         <v>1217</v>
       </c>
@@ -15480,7 +15516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="11" t="s">
         <v>1219</v>
       </c>
@@ -15498,7 +15534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="15" t="s">
         <v>1221</v>
       </c>
@@ -15516,7 +15552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
         <v>1223</v>
       </c>
@@ -15534,7 +15570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="15" t="s">
         <v>1225</v>
       </c>
@@ -15552,7 +15588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>1227</v>
       </c>
@@ -15570,7 +15606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="15" t="s">
         <v>1229</v>
       </c>
@@ -15588,7 +15624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="11" t="s">
         <v>1231</v>
       </c>
@@ -15606,7 +15642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="15" t="s">
         <v>1233</v>
       </c>
@@ -15624,7 +15660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="11" t="s">
         <v>1235</v>
       </c>
@@ -15642,7 +15678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="15" t="s">
         <v>1237</v>
       </c>
@@ -15660,7 +15696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="11" t="s">
         <v>1239</v>
       </c>
@@ -15678,7 +15714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="15" t="s">
         <v>1241</v>
       </c>
@@ -15696,7 +15732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="11" t="s">
         <v>1243</v>
       </c>
@@ -15714,7 +15750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>1245</v>
       </c>
@@ -15732,7 +15768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="11" t="s">
         <v>1247</v>
       </c>
@@ -15750,7 +15786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="15" t="s">
         <v>1249</v>
       </c>
@@ -15768,7 +15804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="11" t="s">
         <v>1251</v>
       </c>
@@ -15786,7 +15822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="15" t="s">
         <v>1253</v>
       </c>
@@ -15804,7 +15840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="11" t="s">
         <v>1255</v>
       </c>
@@ -15822,7 +15858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="15" t="s">
         <v>1257</v>
       </c>
@@ -15840,7 +15876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="11" t="s">
         <v>1259</v>
       </c>
@@ -15858,7 +15894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="15" t="s">
         <v>1261</v>
       </c>
@@ -15876,7 +15912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="11" t="s">
         <v>1263</v>
       </c>
@@ -15894,7 +15930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="15" t="s">
         <v>1265</v>
       </c>
@@ -15923,18 +15959,18 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="55" t="s">
         <v>84</v>
       </c>
@@ -15942,7 +15978,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -15965,7 +16001,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>1267</v>
       </c>
@@ -15980,14 +16016,14 @@
         <v>4</v>
       </c>
       <c r="F3" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="35">
         <f t="shared" ref="G3:G11" si="0">MAX(0,E3-IF(F3="",0,F3))</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>1269</v>
       </c>
@@ -16007,7 +16043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>1271</v>
       </c>
@@ -16029,7 +16065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>1273</v>
       </c>
@@ -16051,7 +16087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>1275</v>
       </c>
@@ -16073,7 +16109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>1277</v>
       </c>
@@ -16095,7 +16131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>1279</v>
       </c>
@@ -16117,7 +16153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>1281</v>
       </c>
@@ -16137,7 +16173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>1283</v>
       </c>
@@ -16168,7 +16204,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G29"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -16178,7 +16214,7 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
         <v>63</v>
       </c>
@@ -16186,7 +16222,7 @@
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16209,7 +16245,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>152</v>
       </c>
@@ -16231,7 +16267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>154</v>
       </c>
@@ -16253,7 +16289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>156</v>
       </c>
@@ -16271,7 +16307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>158</v>
       </c>
@@ -16289,7 +16325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>160</v>
       </c>
@@ -16304,14 +16340,14 @@
         <v>3</v>
       </c>
       <c r="F7" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>161</v>
       </c>
@@ -16333,7 +16369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>163</v>
       </c>
@@ -16355,7 +16391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>165</v>
       </c>
@@ -16373,7 +16409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>167</v>
       </c>
@@ -16391,7 +16427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>169</v>
       </c>
@@ -16413,7 +16449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>171</v>
       </c>
@@ -16433,7 +16469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>173</v>
       </c>
@@ -16451,7 +16487,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>175</v>
       </c>
@@ -16469,7 +16505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>177</v>
       </c>
@@ -16487,7 +16523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>179</v>
       </c>
@@ -16509,7 +16545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>181</v>
       </c>
@@ -16525,7 +16561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>183</v>
       </c>
@@ -16543,7 +16579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>185</v>
       </c>
@@ -16565,7 +16601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>186</v>
       </c>
@@ -16583,7 +16619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>188</v>
       </c>
@@ -16601,7 +16637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>189</v>
       </c>
@@ -16623,7 +16659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>191</v>
       </c>
@@ -16639,7 +16675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>193</v>
       </c>
@@ -16661,7 +16697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>195</v>
       </c>
@@ -16683,7 +16719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>197</v>
       </c>
@@ -16701,7 +16737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>199</v>
       </c>
@@ -16719,7 +16755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>201</v>
       </c>
@@ -16746,7 +16782,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -16756,15 +16792,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
         <v>64</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -16787,7 +16823,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>203</v>
       </c>
@@ -16805,7 +16841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>205</v>
       </c>
@@ -16819,13 +16855,15 @@
       <c r="E4" s="14">
         <v>2</v>
       </c>
-      <c r="F4" s="31"/>
+      <c r="F4" s="31">
+        <v>1</v>
+      </c>
       <c r="G4" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>207</v>
       </c>
@@ -16843,7 +16881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>208</v>
       </c>
@@ -16865,7 +16903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>210</v>
       </c>
@@ -16883,7 +16921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>212</v>
       </c>
@@ -16899,7 +16937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>214</v>
       </c>
@@ -16915,7 +16953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>216</v>
       </c>
@@ -16933,7 +16971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>218</v>
       </c>
@@ -16953,7 +16991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>220</v>
       </c>
@@ -16975,7 +17013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>222</v>
       </c>
@@ -16993,7 +17031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>224</v>
       </c>
@@ -17015,7 +17053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>226</v>
       </c>
@@ -17035,7 +17073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>228</v>
       </c>
@@ -17057,7 +17095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>230</v>
       </c>
@@ -17079,7 +17117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>232</v>
       </c>
@@ -17101,7 +17139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>233</v>
       </c>
@@ -17121,7 +17159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>235</v>
       </c>
@@ -17143,7 +17181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>237</v>
       </c>
@@ -17161,7 +17199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>239</v>
       </c>
@@ -17179,7 +17217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>241</v>
       </c>
@@ -17197,7 +17235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>243</v>
       </c>
@@ -17213,7 +17251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>245</v>
       </c>
@@ -17235,7 +17273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>246</v>
       </c>
@@ -17253,7 +17291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>248</v>
       </c>
@@ -17271,7 +17309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>250</v>
       </c>
@@ -17298,7 +17336,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -17308,15 +17346,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
         <v>65</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17339,7 +17377,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>252</v>
       </c>
@@ -17357,7 +17395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>254</v>
       </c>
@@ -17379,7 +17417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>256</v>
       </c>
@@ -17397,7 +17435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>257</v>
       </c>
@@ -17419,7 +17457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>259</v>
       </c>
@@ -17441,7 +17479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>261</v>
       </c>
@@ -17461,7 +17499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>263</v>
       </c>
@@ -17477,7 +17515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>265</v>
       </c>
@@ -17495,7 +17533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>267</v>
       </c>
@@ -17517,7 +17555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>269</v>
       </c>
@@ -17539,7 +17577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>271</v>
       </c>
@@ -17557,7 +17595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>273</v>
       </c>
@@ -17579,7 +17617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>275</v>
       </c>
@@ -17599,7 +17637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>277</v>
       </c>
@@ -17617,7 +17655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>279</v>
       </c>
@@ -17635,7 +17673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>281</v>
       </c>
@@ -17651,7 +17689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>283</v>
       </c>
@@ -17671,7 +17709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>285</v>
       </c>
@@ -17693,7 +17731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>287</v>
       </c>
@@ -17715,7 +17753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>289</v>
       </c>
@@ -17730,14 +17768,14 @@
         <v>2</v>
       </c>
       <c r="F22" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>291</v>
       </c>
@@ -17755,7 +17793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>292</v>
       </c>
@@ -17773,7 +17811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>294</v>
       </c>
@@ -17791,7 +17829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>295</v>
       </c>
@@ -17809,7 +17847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>297</v>
       </c>
@@ -17838,7 +17876,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -17848,15 +17886,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
         <v>66</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -17879,7 +17917,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>299</v>
       </c>
@@ -17897,7 +17935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>301</v>
       </c>
@@ -17919,7 +17957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>303</v>
       </c>
@@ -17937,7 +17975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>305</v>
       </c>
@@ -17959,7 +17997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>307</v>
       </c>
@@ -17981,7 +18019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>309</v>
       </c>
@@ -18003,7 +18041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>311</v>
       </c>
@@ -18025,7 +18063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>313</v>
       </c>
@@ -18041,7 +18079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>315</v>
       </c>
@@ -18063,7 +18101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>317</v>
       </c>
@@ -18081,7 +18119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>319</v>
       </c>
@@ -18099,7 +18137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>321</v>
       </c>
@@ -18117,7 +18155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>323</v>
       </c>
@@ -18135,7 +18173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>325</v>
       </c>
@@ -18157,7 +18195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>327</v>
       </c>
@@ -18175,7 +18213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>328</v>
       </c>
@@ -18193,7 +18231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>330</v>
       </c>
@@ -18209,7 +18247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>332</v>
       </c>
@@ -18231,7 +18269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>333</v>
       </c>
@@ -18249,7 +18287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>334</v>
       </c>
@@ -18271,7 +18309,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>336</v>
       </c>
@@ -18289,7 +18327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>338</v>
       </c>
@@ -18309,7 +18347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>340</v>
       </c>
@@ -18331,7 +18369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>342</v>
       </c>
@@ -18349,7 +18387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>344</v>
       </c>
@@ -18376,7 +18414,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -18386,15 +18424,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="42" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -18417,7 +18455,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>346</v>
       </c>
@@ -18435,7 +18473,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>348</v>
       </c>
@@ -18457,7 +18495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>350</v>
       </c>
@@ -18475,7 +18513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>351</v>
       </c>
@@ -18493,7 +18531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>353</v>
       </c>
@@ -18515,7 +18553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>355</v>
       </c>
@@ -18531,7 +18569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>357</v>
       </c>
@@ -18546,14 +18584,14 @@
         <v>3</v>
       </c>
       <c r="F9" s="31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>359</v>
       </c>
@@ -18569,7 +18607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>361</v>
       </c>
@@ -18587,7 +18625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>363</v>
       </c>
@@ -18609,7 +18647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>365</v>
       </c>
@@ -18625,7 +18663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>367</v>
       </c>
@@ -18647,7 +18685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>369</v>
       </c>
@@ -18665,7 +18703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>371</v>
       </c>
@@ -18685,7 +18723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>373</v>
       </c>
@@ -18703,7 +18741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>375</v>
       </c>
@@ -18721,7 +18759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>376</v>
       </c>
@@ -18739,7 +18777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>378</v>
       </c>
@@ -18761,7 +18799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>380</v>
       </c>
@@ -18783,7 +18821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>382</v>
       </c>
@@ -18797,13 +18835,15 @@
       <c r="E22" s="14">
         <v>1</v>
       </c>
-      <c r="F22" s="31"/>
+      <c r="F22" s="31">
+        <v>1</v>
+      </c>
       <c r="G22" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>384</v>
       </c>
@@ -18825,7 +18865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>386</v>
       </c>
@@ -18838,14 +18878,14 @@
         <v>2</v>
       </c>
       <c r="F24" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G24" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>388</v>
       </c>
@@ -18863,7 +18903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>390</v>
       </c>
@@ -18881,7 +18921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>392</v>
       </c>
@@ -18901,7 +18941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>394</v>
       </c>
@@ -18919,7 +18959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>396</v>
       </c>
@@ -18937,7 +18977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="15" t="s">
         <v>398</v>
       </c>
@@ -18964,7 +19004,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:G28"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -18974,15 +19014,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="43" t="s">
         <v>68</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -19005,7 +19045,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>400</v>
       </c>
@@ -19020,14 +19060,14 @@
         <v>3</v>
       </c>
       <c r="F3" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G3" s="35">
         <f t="shared" ref="G3:G28" si="0">MAX(0,E3-IF(F3="",0,F3))</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>402</v>
       </c>
@@ -19045,7 +19085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>404</v>
       </c>
@@ -19063,7 +19103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>405</v>
       </c>
@@ -19081,7 +19121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>407</v>
       </c>
@@ -19099,7 +19139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>408</v>
       </c>
@@ -19117,7 +19157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>410</v>
       </c>
@@ -19135,7 +19175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>412</v>
       </c>
@@ -19155,7 +19195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>414</v>
       </c>
@@ -19175,7 +19215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>416</v>
       </c>
@@ -19193,7 +19233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>418</v>
       </c>
@@ -19215,7 +19255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>420</v>
       </c>
@@ -19233,7 +19273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>422</v>
       </c>
@@ -19251,7 +19291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>424</v>
       </c>
@@ -19269,7 +19309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>426</v>
       </c>
@@ -19287,7 +19327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>428</v>
       </c>
@@ -19307,7 +19347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>430</v>
       </c>
@@ -19329,7 +19369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>432</v>
       </c>
@@ -19349,7 +19389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>434</v>
       </c>
@@ -19367,7 +19407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>436</v>
       </c>
@@ -19385,7 +19425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>437</v>
       </c>
@@ -19403,7 +19443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>439</v>
       </c>
@@ -19425,7 +19465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>441</v>
       </c>
@@ -19445,7 +19485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>443</v>
       </c>
@@ -19463,7 +19503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11" t="s">
         <v>445</v>
       </c>
@@ -19481,7 +19521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="15" t="s">
         <v>447</v>
       </c>
@@ -19508,7 +19548,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
@@ -19518,15 +19558,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="44" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
       <c r="D1" s="37"/>
     </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -19549,7 +19589,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>449</v>
       </c>
@@ -19567,7 +19607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>451</v>
       </c>
@@ -19585,7 +19625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>453</v>
       </c>
@@ -19600,14 +19640,14 @@
         <v>3</v>
       </c>
       <c r="F5" s="31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" s="35">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="15" t="s">
         <v>454</v>
       </c>
@@ -19625,7 +19665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>456</v>
       </c>
@@ -19643,7 +19683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>458</v>
       </c>
@@ -19661,7 +19701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>460</v>
       </c>
@@ -19683,7 +19723,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>462</v>
       </c>
@@ -19705,7 +19745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>464</v>
       </c>
@@ -19725,7 +19765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>466</v>
       </c>
@@ -19747,7 +19787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>468</v>
       </c>
@@ -19765,7 +19805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
         <v>469</v>
       </c>
@@ -19783,7 +19823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>471</v>
       </c>
@@ -19803,7 +19843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>473</v>
       </c>
@@ -19821,7 +19861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>475</v>
       </c>
@@ -19843,7 +19883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="15" t="s">
         <v>477</v>
       </c>
@@ -19861,7 +19901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>478</v>
       </c>
@@ -19883,7 +19923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="15" t="s">
         <v>480</v>
       </c>
@@ -19901,7 +19941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>482</v>
       </c>
@@ -19923,7 +19963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
         <v>484</v>
       </c>
@@ -19941,7 +19981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>486</v>
       </c>
@@ -19959,7 +19999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="15" t="s">
         <v>488</v>
       </c>
@@ -19981,7 +20021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11" t="s">
         <v>489</v>
       </c>
@@ -19999,7 +20039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="15" t="s">
         <v>491</v>
       </c>

--- a/Liga 2021-22/cromos_laliga.xlsx
+++ b/Liga 2021-22/cromos_laliga.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Documents\Cromos\Liga 2021-22\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571CFE18-4969-4361-840A-15F63AA41E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7777CF4-0023-40D7-9C34-A76519E7E21C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="19" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="20" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -4391,7 +4391,7 @@
     <xf numFmtId="0" fontId="3" fillId="37" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -4402,6 +4402,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -4441,9 +4444,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5375,11 +5375,11 @@
       </c>
       <c r="F23" s="28">
         <f>SUM('LEYENDAS LaLiga'!F3:F34)</f>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" s="33">
         <f>SUM('LEYENDAS LaLiga'!G3:G34)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -5488,11 +5488,11 @@
       </c>
       <c r="F27" s="30">
         <f t="shared" si="0"/>
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G27" s="34">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -5529,7 +5529,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>70</v>
       </c>
       <c r="B1" s="37"/>
@@ -6079,7 +6079,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>71</v>
       </c>
       <c r="B1" s="37"/>
@@ -6611,7 +6611,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="48" t="s">
         <v>72</v>
       </c>
       <c r="B1" s="37"/>
@@ -7197,7 +7197,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
         <v>73</v>
       </c>
       <c r="B1" s="37"/>
@@ -7707,7 +7707,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="49" t="s">
         <v>74</v>
       </c>
       <c r="B1" s="37"/>
@@ -8239,7 +8239,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="50" t="s">
         <v>75</v>
       </c>
       <c r="B1" s="37"/>
@@ -8807,7 +8807,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
         <v>76</v>
       </c>
       <c r="B1" s="37"/>
@@ -9319,7 +9319,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
         <v>77</v>
       </c>
       <c r="B1" s="37"/>
@@ -9861,7 +9861,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="51" t="s">
         <v>78</v>
       </c>
       <c r="B1" s="37"/>
@@ -10429,7 +10429,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="47" t="s">
         <v>79</v>
       </c>
       <c r="B1" s="37"/>
@@ -12382,7 +12382,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="52" t="s">
         <v>80</v>
       </c>
       <c r="B1" s="37"/>
@@ -12912,7 +12912,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="37"/>
@@ -13446,7 +13446,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="44" t="s">
         <v>81</v>
       </c>
       <c r="B1" s="37"/>
@@ -13962,7 +13962,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="54" t="s">
         <v>82</v>
       </c>
       <c r="B1" s="37"/>
@@ -14295,11 +14295,11 @@
         <v>4</v>
       </c>
       <c r="F17" s="31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G17" s="35">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -14678,7 +14678,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="36" t="s">
         <v>83</v>
       </c>
       <c r="B1" s="37"/>
@@ -16793,7 +16793,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
         <v>64</v>
       </c>
       <c r="B1" s="37"/>
@@ -17347,7 +17347,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="41" t="s">
         <v>65</v>
       </c>
       <c r="B1" s="37"/>
@@ -17887,7 +17887,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="42" t="s">
         <v>66</v>
       </c>
       <c r="B1" s="37"/>
@@ -18425,7 +18425,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="43" t="s">
         <v>67</v>
       </c>
       <c r="B1" s="37"/>
@@ -19015,7 +19015,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="44" t="s">
         <v>68</v>
       </c>
       <c r="B1" s="37"/>
@@ -19559,7 +19559,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="45" t="s">
         <v>69</v>
       </c>
       <c r="B1" s="37"/>
